--- a/src/attributions/attributions_ig_traj_348.xlsx
+++ b/src/attributions/attributions_ig_traj_348.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07573856821124531</v>
+        <v>0.0230642411328944</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000478680001245514</v>
+        <v>-0.004370203340320985</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.008316404473654383</v>
+        <v>-0.001734360686104043</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09836669271709855</v>
+        <v>0.06198800103290953</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0002778821151272864</v>
+        <v>-0.01931798051012267</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1050,25 +1050,25 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.05740874092375272</v>
+        <v>-0.003418696434027436</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07951447024739033</v>
+        <v>0.009441646877918276</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09298330089253222</v>
+        <v>-0.03090784597945822</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
@@ -1077,40 +1077,40 @@
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01353500513693108</v>
+        <v>-0.001581151475387575</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03264927012243203</v>
+        <v>-0.01007716925297012</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02024464726756917</v>
+        <v>-0.01000629400485051</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.005743843695370463</v>
+        <v>0.004717121324789297</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04729515823161903</v>
+        <v>0.01799086442809119</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,34 +1119,34 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0261750947833627</v>
+        <v>-0.003136091090114081</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.03919381070690776</v>
+        <v>-0.008308756742889709</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3633023797772357</v>
+        <v>0.1326069470487309</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2512189145329169</v>
+        <v>-0.02956953784329374</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.04983543231476969</v>
+        <v>-0.001670298792177896</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02521490106465831</v>
+        <v>-0.009788584721752765</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,61 +1173,61 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.06648996996736338</v>
+        <v>-0.01530918515239674</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.08594334345751509</v>
+        <v>-0.01988649352620503</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.07041384294744212</v>
+        <v>0.009718486209136065</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1708761119269333</v>
+        <v>0.05174773836907767</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.05958087930456844</v>
+        <v>0.0178502318262557</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1864600049848607</v>
+        <v>0.06554811996098116</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.02720594209817652</v>
+        <v>-0.01844526990512472</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,55 +1236,55 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.0519240556239732</v>
+        <v>-0.01039971719733651</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.08112817089125839</v>
+        <v>-0.03425213204327496</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.008294761419031323</v>
+        <v>0.009740699918575912</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.05467951716555275</v>
+        <v>0.01320642982710561</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.006309376385439955</v>
+        <v>-0.005985676666072259</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.01353296186474454</v>
+        <v>0.0007622569694603662</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,40 +1293,40 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0004864446306011638</v>
+        <v>0.0008574535233753048</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.08944280910430522</v>
+        <v>-0.03547279314543856</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01212876410177994</v>
+        <v>0.006131021895328988</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.03522603493223619</v>
+        <v>0.01531618738164607</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.08091822206673489</v>
+        <v>-0.05413231320633</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
@@ -1335,25 +1335,25 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01854015268669421</v>
+        <v>0.003546743595321557</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.02568279896971423</v>
+        <v>-0.0009910418245419527</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.03159189478327976</v>
+        <v>-0.0176385133212382</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.05140187717545644</v>
+        <v>0.02611702271918252</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
@@ -1374,25 +1374,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.007347029892931158</v>
+        <v>0.01055859429741718</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1198600863995816</v>
+        <v>-0.02143602858854228</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.06906414327214179</v>
+        <v>-0.00596561837445763</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,67 +1401,67 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.06040055459988612</v>
+        <v>-0.01385861981455702</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.07535727909893548</v>
+        <v>-0.02524849850797377</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.02132084440839756</v>
+        <v>-0.008931858794992914</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.09856164949329732</v>
+        <v>0.01326268701662488</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.06685110802788137</v>
+        <v>-0.005650037606991096</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03336928061897614</v>
+        <v>0.001438921507582728</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.08354238223963802</v>
+        <v>0.01594915814652776</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.09599835113385584</v>
+        <v>-0.04371512349291928</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
@@ -1470,25 +1470,25 @@
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.008646122839700459</v>
+        <v>0.002121815234176583</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.03679783562353432</v>
+        <v>0.01232147898241949</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03259445079046676</v>
+        <v>0.03562355453779131</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,25 +1497,25 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1070613209286315</v>
+        <v>0.007751628794590318</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.006662145308892503</v>
+        <v>0.03157494221675025</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01965557068570571</v>
+        <v>-0.004005160283218483</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,7 +1524,7 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.01175218821887234</v>
+        <v>0.002303361996410938</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
@@ -1536,13 +1536,13 @@
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.02764290475701971</v>
+        <v>-0.007585887546443576</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.06398886449753673</v>
+        <v>-0.02299334916097832</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,19 +1551,19 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.0888424668266049</v>
+        <v>-0.003364833232782581</v>
       </c>
     </row>
     <row r="3">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1456839211514797</v>
+        <v>0.00101565619207446</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,16 +2718,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007019995131012038</v>
+        <v>3.876961786800372e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0348560714663351</v>
+        <v>-8.283898390000788e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,25 +2736,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1612515046311658</v>
+        <v>0.002421666249955447</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008919166770398279</v>
+        <v>-3.038023390619159e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.06151659595668091</v>
+        <v>-0.0004648570262004973</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,49 +2763,49 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1059754179018192</v>
+        <v>0.0006710002019465617</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1293372633758022</v>
+        <v>-0.002041613223024548</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.01137106196058207</v>
+        <v>-0.0003715763334996888</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05036791138715228</v>
+        <v>-0.0001749233593741056</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.003017014811925896</v>
+        <v>-0.0003568253690801718</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0006116257423711823</v>
+        <v>-0.0001282064406515761</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,10 +2814,10 @@
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0378211119425077</v>
+        <v>0.0006343760843263322</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,52 +2826,52 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.05468071147151903</v>
+        <v>0.0002812771096520189</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.05253515466430465</v>
+        <v>-0.0003960821243699694</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3152710242283234</v>
+        <v>0.005168650793937381</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2723810703161728</v>
+        <v>-0.0007826635889328851</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.13288205426974</v>
+        <v>-0.0003164691345037652</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02096342756028269</v>
+        <v>-0.001043478885405898</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1150222220297042</v>
+        <v>-0.0007975253725578159</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.008249788287343436</v>
+        <v>0.0001542353244151424</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.09813345969390337</v>
+        <v>0.001866348432508579</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,13 +2907,13 @@
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.06747357917422028</v>
+        <v>0.002274456622518244</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.08091866198941465</v>
+        <v>-0.001121525825225353</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,34 +2925,34 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1541422805246134</v>
+        <v>0.002777834883320566</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1269486415455983</v>
+        <v>-0.0007118173316858089</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.06821928795145235</v>
+        <v>0.0001624085303218192</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.09930064298814943</v>
+        <v>-0.0006017440772122843</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
@@ -2961,16 +2961,16 @@
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.00775702566304565</v>
+        <v>-0.0002287296490698349</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.03800833397579291</v>
+        <v>0.0002874404129750098</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,34 +2979,34 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001606455925646153</v>
+        <v>-0.0006316543342640103</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.03097985535778277</v>
+        <v>0.0002410832136143954</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.007224657393728026</v>
+        <v>1.274848856311575e-05</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1086954120369406</v>
+        <v>-0.0007176002367612514</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03038566501797262</v>
+        <v>-0.0004143067669859706</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.04596778765785167</v>
+        <v>0.0004708884045853199</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.06699575927271648</v>
+        <v>-0.002025373700656727</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08222163819467267</v>
+        <v>-0.001712479402524628</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.03751528662767125</v>
+        <v>-6.135208384709953e-05</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
@@ -3057,25 +3057,25 @@
         <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0006778493548603449</v>
+        <v>-0.0004856218338922727</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.05610061857016682</v>
+        <v>-0.000117460898953707</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.01308885959260702</v>
+        <v>0.00174102059815628</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
@@ -3087,34 +3087,34 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.141000031011637</v>
+        <v>-0.0002113110594584764</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02517172784887232</v>
+        <v>-0.001514234959018723</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.02518934955743813</v>
+        <v>0.0005523637327720214</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.07731268723237493</v>
+        <v>-0.0006755023650128138</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
@@ -3123,16 +3123,16 @@
         <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03393434822428795</v>
+        <v>-0.000451153459559144</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.056092974539629</v>
+        <v>-0.0001431979925361142</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.07831623332410131</v>
+        <v>-9.223399975444112e-05</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1112028557580193</v>
+        <v>0.0003337774603431214</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.02631446050626329</v>
+        <v>0.0009483441423234984</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1085796861599142</v>
+        <v>-0.001222747256899893</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,13 +3177,13 @@
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04688224056743139</v>
+        <v>-0.000429930971623891</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.04758816507193727</v>
+        <v>0.0004042188807369086</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3195,7 +3195,7 @@
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.004902250625741452</v>
+        <v>0.001026503194803009</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
@@ -3204,70 +3204,70 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.07309690290363155</v>
+        <v>-0.0005174968822968145</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0.00637798316184528</v>
+        <v>-1.402995261780974e-06</v>
       </c>
       <c r="FN5" t="n">
         <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01233943440136476</v>
+        <v>1.482429379424689e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001688817940660875</v>
+        <v>0.0003767929916280551</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0383181622230787</v>
+        <v>-0.0002811227934271415</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.05905891350312934</v>
+        <v>-0.0007088385248575894</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.03573465439756787</v>
+        <v>0.0006715916322775564</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.308136041568655</v>
+        <v>0.4680135213328546</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.246979541901954</v>
+        <v>-0.249484502375724</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001418305825317624</v>
+        <v>0.0006948715989825681</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2820396920712785</v>
+        <v>0.5893300186197082</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1898442081304796</v>
+        <v>-0.2376903082257765</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04438314547111684</v>
+        <v>-0.07407027648037866</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1863711960531554</v>
+        <v>0.3188882536532863</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.03245113711132101</v>
+        <v>-0.06518635726110371</v>
       </c>
       <c r="W7" t="n">
-        <v>0.145548781867915</v>
+        <v>0.01075425273665464</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,28 +3925,28 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03480821812840731</v>
+        <v>-0.03298408473697743</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002781491789784687</v>
+        <v>0.1458752589810768</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.009919946858551429</v>
+        <v>-0.02541284935582946</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3955,43 +3955,43 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03767580068383242</v>
+        <v>0.3185415225150591</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.09125961872095562</v>
+        <v>-0.1886198107270233</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06676844220371166</v>
+        <v>0.2649094524467833</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5489202953699498</v>
+        <v>0.8543505013760248</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1290745349497014</v>
+        <v>-0.411010394584692</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1636374207254766</v>
+        <v>-0.2486532626035955</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0561073505034549</v>
+        <v>-0.01150079128210187</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1272971252237194</v>
+        <v>-0.1590433572063247</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1179612876189809</v>
+        <v>-0.1256984815331091</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05334062555852546</v>
+        <v>-0.116222839428088</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0532781039061477</v>
+        <v>0.04570715386983926</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1882309561883448</v>
+        <v>0.06005063771948244</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
@@ -4063,16 +4063,16 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2680978234446056</v>
+        <v>0.7314189974110187</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.05079859067566444</v>
+        <v>-0.2054143979684063</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1276664921846821</v>
+        <v>0.01227499292435315</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -4081,31 +4081,31 @@
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1224368969974488</v>
+        <v>-0.3353566217177941</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05188857132559846</v>
+        <v>0.2587892856792918</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03454128338347627</v>
+        <v>-0.08663755705216339</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,49 +4117,49 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.00398082907903584</v>
+        <v>-0.1975366409507522</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.06933921517193167</v>
+        <v>0.3666171375945244</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0810868990527604</v>
+        <v>0.09917944216406015</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1156062459157742</v>
+        <v>-0.3373041944074143</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.08205920303793832</v>
+        <v>0.2501803921340847</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.03955027220541803</v>
+        <v>-0.05785004250337372</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1128934867186368</v>
+        <v>-0.5069218621652868</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.04399754718010405</v>
+        <v>0.1386554424265235</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.05508072600522133</v>
+        <v>-0.09345930652115762</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01308922988748438</v>
+        <v>-0.1074132598729806</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.08704078079537347</v>
+        <v>0.07242624325862036</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.1098382042861213</v>
+        <v>0.003328859883093331</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,25 +4225,25 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04924936518695596</v>
+        <v>0.1092378561718847</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.0311825530133635</v>
+        <v>-0.2776010064695211</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03246154201041541</v>
+        <v>-0.2847400710678546</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,22 +4252,22 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1058295024999718</v>
+        <v>-0.3027354151073762</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07708542364148763</v>
+        <v>0.2134120341277718</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.05794504266960257</v>
+        <v>-0.01748315027900779</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,25 +4276,25 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1396256541959134</v>
+        <v>-0.2236461961291064</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.06232282006589054</v>
+        <v>0.06915527532765653</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.02467415193067227</v>
+        <v>0.01946410205850446</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,25 +4303,25 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1209171992911096</v>
+        <v>-0.4019723485871931</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.05664225252624153</v>
+        <v>0.3151540098875595</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03895755471164623</v>
+        <v>-0.080904754107667</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,49 +4330,49 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03402184132564226</v>
+        <v>-0.2501276305276404</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.09382094824954623</v>
+        <v>0.1725638213341054</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01860101454586399</v>
+        <v>0.02014947461920463</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.02151819083240892</v>
+        <v>-0.05391067501886608</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.07911482123993194</v>
+        <v>0.1585738216096483</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.005858280160383282</v>
+        <v>0.03324205013323243</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.04637325522405137</v>
+        <v>-0.3808290367061347</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1171996280644711</v>
+        <v>0.1442058248352464</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2553323292486331</v>
+        <v>0.476492105399981</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06035569036219256</v>
+        <v>0.0140547868978985</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1405023945453774</v>
+        <v>-0.1225296311014108</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,25 +4443,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1963461923007995</v>
+        <v>0.6188913633125106</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04421655169414063</v>
+        <v>-0.1009640950618155</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2470126368590713</v>
+        <v>-0.1432426776682864</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08151067089495979</v>
+        <v>0.1708751561789835</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,64 +4479,64 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.06290113827107999</v>
+        <v>-0.1303637369365144</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02800001905935462</v>
+        <v>-0.0387503622811611</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01989540174974715</v>
+        <v>0.01210480274458175</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01308862025146248</v>
+        <v>-0.0643734057630875</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004597412030669789</v>
+        <v>-0.05142357542033883</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.07498654663952052</v>
+        <v>0.2655264258863291</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.004162330227686552</v>
+        <v>0.1976583155090205</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.09621699459964303</v>
+        <v>-0.2520540588974006</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3810597779702696</v>
+        <v>1.053481743331629</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1339831952535404</v>
+        <v>-0.2871762390817434</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.2984109151148688</v>
+        <v>-0.3004833718961756</v>
       </c>
       <c r="AZ8" t="n">
         <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.09382221172000745</v>
+        <v>-0.003713678728142966</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.07930957121456964</v>
+        <v>-0.08913769400614485</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.05496398359694169</v>
+        <v>-0.1097176741850608</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.09085908738331115</v>
+        <v>0.01243717642068739</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.005913677274176876</v>
+        <v>0.1822985436784725</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01648157093132357</v>
+        <v>0.02759170752917412</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1748125593362344</v>
+        <v>0.7190990604342494</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.09986797577448973</v>
+        <v>-0.1176140074313322</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.1215082261820448</v>
+        <v>-0.2358161497799062</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4653,67 +4653,67 @@
         <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.09444803992882324</v>
+        <v>-0.3277859396173685</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01186001075146671</v>
+        <v>-0.007100769985337612</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.1035957028969557</v>
+        <v>0.1643421886563396</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.0002878623807203</v>
+        <v>-0.2684713821919001</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.02942368232175689</v>
+        <v>0.1200566679299594</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.005337961829377705</v>
+        <v>0.1881780249046533</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.07921731318496898</v>
+        <v>-0.3246944754597573</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.005785932381349564</v>
+        <v>-0.03104865237890815</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.1187519738825575</v>
+        <v>0.1453030851360523</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.0238254309452103</v>
+        <v>-0.04320787395201089</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,43 +4749,43 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06375818220772057</v>
+        <v>-0.2940009970660832</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0.06245362777140466</v>
+        <v>0.04295210393743862</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.007144762344660035</v>
+        <v>-0.1405159963822276</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02002437030255545</v>
+        <v>-0.00586608528677242</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.01367269124875494</v>
+        <v>0.02122720085642914</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,19 +4794,19 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.05682305866219151</v>
+        <v>0.07764953988764782</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01998850327167285</v>
+        <v>-0.05785102285102073</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.08184701509984406</v>
+        <v>-0.1541061029992307</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4818,22 +4818,22 @@
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.074837383831558</v>
+        <v>-0.06773138121605939</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01914074450782193</v>
+        <v>-0.1119831007122527</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.1128541724024182</v>
+        <v>0.03538139899119523</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4845,103 +4845,103 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.02950308962608741</v>
+        <v>-0.1755185101552535</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.02162450000639929</v>
+        <v>-0.2244022078820907</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.04860572160368239</v>
+        <v>0.07093507040352207</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.07519737562396658</v>
+        <v>-0.3545262251366729</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.003634813535722961</v>
+        <v>-0.05596250195159911</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.1034465240717119</v>
+        <v>0.1361125386945142</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.04531451440036609</v>
+        <v>-0.367828062792797</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03193724451937031</v>
+        <v>0.1327007502482133</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.08666481688870464</v>
+        <v>0.1595727133736484</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.01582527408402181</v>
+        <v>-0.08336369006428532</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.01524935124616478</v>
+        <v>0.02425516918040202</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.07052617018832834</v>
+        <v>0.1517850994021259</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4953,13 +4953,13 @@
         <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.003380327058767873</v>
+        <v>-0.1005765093146997</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.05527249178258466</v>
+        <v>-0.08494520331526866</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,7 +4977,7 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1033987582074574</v>
+        <v>0.01444202208378105</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,34 +5563,34 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.06180872139991046</v>
+        <v>-0.006372709700266823</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01591426624679503</v>
+        <v>0.002606077808778397</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09164053826427862</v>
+        <v>0.01764586628574095</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.04905786988559949</v>
+        <v>-0.0119962733022142</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,16 +5599,16 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.04879486110389886</v>
+        <v>0.001277480163123275</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1012258459267559</v>
+        <v>0.01038754458324826</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02310199215796888</v>
+        <v>-0.01304183918353601</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
@@ -5626,79 +5626,79 @@
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0408153618320814</v>
+        <v>-0.003618570533686965</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02288544059169746</v>
+        <v>0.0003301335320383845</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.02311497268495512</v>
+        <v>-0.004105591911703655</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.002819277496495619</v>
+        <v>0.002690385125179365</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.05190999538630606</v>
+        <v>0.01116645456102967</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02447071518995486</v>
+        <v>-0.004047152028375867</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.02637654038119692</v>
+        <v>0.002782815559263653</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2566512383833651</v>
+        <v>0.04034155121685012</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.03413403374083424</v>
+        <v>-0.02083606486236421</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.05089016452021177</v>
+        <v>-0.0001685378131255292</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.0363734537201918</v>
+        <v>-0.007451692579979107</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1036487993020915</v>
+        <v>-0.01124972975750465</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.05424439728912034</v>
+        <v>0.0009699543218663041</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.06241268488734149</v>
+        <v>0.01429020094660464</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,43 +5752,43 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02984530240879427</v>
+        <v>0.009553680441010362</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.008823618188773162</v>
+        <v>-0.002919646762520154</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.158269913482134</v>
+        <v>0.02694688679624492</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01880301415026433</v>
+        <v>-0.01219962595645383</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.03197641412843023</v>
+        <v>-0.003699113049723575</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,7 +5797,7 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.03822577257145659</v>
+        <v>-0.005746507892048934</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
@@ -5806,52 +5806,52 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0190978413591189</v>
+        <v>0.004232496154110127</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.002160569622381371</v>
+        <v>-0.00124942777078826</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.02253269881005172</v>
+        <v>-0.007117947966358638</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.04403029298305127</v>
+        <v>0.01183848548930854</v>
       </c>
       <c r="CR10" t="n">
         <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0008816007444548573</v>
+        <v>0.003109681383246473</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02673163825032252</v>
+        <v>-0.005271136139131917</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
@@ -5860,43 +5860,43 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.004963392188269864</v>
+        <v>0.003866772368234405</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.002630574243376753</v>
+        <v>0.0006580641554077552</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.120113232045637</v>
+        <v>0.001514877196155079</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01277067501244165</v>
+        <v>-0.00384817396506892</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.01459758004107834</v>
+        <v>-0.0004909382858904396</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,7 +5905,7 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.005541938693666868</v>
+        <v>-0.009047138000656868</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
@@ -5914,43 +5914,43 @@
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.006566740069972578</v>
+        <v>-0.003037112837820344</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.01689898466044384</v>
+        <v>0.003521208797200295</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04715619769001198</v>
+        <v>0.005289282365695973</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.04924664737267104</v>
+        <v>-0.01049372840856284</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.009089230947277914</v>
+        <v>-0.005104449005696489</v>
       </c>
       <c r="EE10" t="n">
         <v>0</v>
@@ -5959,16 +5959,16 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.007932857724687221</v>
+        <v>0.0002063522865280001</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03575489206650671</v>
+        <v>-0.005077271736875233</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,43 +5977,43 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.02529207986816507</v>
+        <v>-0.001289140445110197</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05818188113843341</v>
+        <v>0.0005232747350789701</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01706992689060513</v>
+        <v>-0.002090253073304271</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.04654975367123194</v>
+        <v>-0.0001602661061294353</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.03345131591073507</v>
+        <v>-0.007304898864355134</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,25 +6022,25 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.002186820400608861</v>
+        <v>0.002823312822479594</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001980597510450248</v>
+        <v>0.0006007753049418192</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.03030582885566441</v>
+        <v>0.001040240035506305</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,7 +6049,7 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01474060629656515</v>
+        <v>0.007280243878984505</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.03143877613056822</v>
+        <v>-0.009332995058960163</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
@@ -6067,7 +6067,7 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001465884914252954</v>
+        <v>-0.001065802677524361</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,28 +6076,28 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.005081431625724553</v>
+        <v>0.002200834181319083</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.01651565299580694</v>
+        <v>0.0002907606290217093</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.06352783391278963</v>
+        <v>-0.005721482724779755</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,13 +6106,13 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.03330224257608763</v>
+        <v>-0.003378543368922086</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,19 +6120,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1129286508972713</v>
+        <v>-0.04964802002669524</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3934606958369784</v>
+        <v>0.07275673683715357</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1205523579464054</v>
+        <v>-0.02200307713012989</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6147,91 +6147,91 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.06755002786734846</v>
+        <v>-0.03577376604973211</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2559820835806024</v>
+        <v>0.08356688250007063</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1800152427255538</v>
+        <v>-0.02579302254368446</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01623293358140101</v>
+        <v>0.01468003042723692</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2671674238197894</v>
+        <v>0.01123473141545783</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05303149412720707</v>
+        <v>-0.0009956596072438725</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.920768793610937e-11</v>
+        <v>-2.860500386986701e-12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03921351927060709</v>
+        <v>0.002106912123971353</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.0003379980955681565</v>
+        <v>-0.004300003081365542</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.06806368198932924</v>
+        <v>-0.004587767894531822</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2089998724990556</v>
+        <v>0.03330645312320941</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,52 +6240,52 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.05737450468985338</v>
+        <v>-0.007081018326720091</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.09071032357272926</v>
+        <v>-0.01579562547720512</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.541667417840325</v>
+        <v>0.0829297326132057</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1617179785343792</v>
+        <v>-0.047224109377603</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.05722529226282546</v>
+        <v>-0.04115212416409791</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.04634216462226342</v>
+        <v>0.01260427884480699</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.3282327371717088</v>
+        <v>-0.01713676242388487</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.005689404964449868</v>
+        <v>0.01202441888059377</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.02899987122844675</v>
+        <v>0.02051448575655197</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.06134513232691902</v>
+        <v>0.04468013579052404</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,10 +6336,10 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.08185553423724622</v>
+        <v>0.0004013815268035167</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4141928545992247</v>
+        <v>0.07216927596852178</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,52 +6348,52 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01895599535333535</v>
+        <v>-0.01422802444566506</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.03608559607893798</v>
+        <v>0.02862904698511616</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1042034095633602</v>
+        <v>-0.03794383135620361</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.003311361857313077</v>
+        <v>0.0008801322124160736</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.09765670836580827</v>
+        <v>0.007790452932302053</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.008757178829219758</v>
+        <v>-0.03069467210320854</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.06049236545915489</v>
+        <v>0.002129376135152895</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
@@ -6414,121 +6414,121 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01867878896234685</v>
+        <v>0.02591904748492205</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1128188374858225</v>
+        <v>-0.03822329516085848</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.004028395428125664</v>
+        <v>-0.002379805447057993</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.04992623904213585</v>
+        <v>0.01096033490386043</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.1971872018027434</v>
+        <v>-0.05860883892634262</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08017515092536989</v>
+        <v>-0.02140967540353253</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.07613377232160144</v>
+        <v>-0.01737084236476124</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.07353923112270259</v>
+        <v>-0.02833085339559912</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.01599533748582309</v>
+        <v>0.0001510358237184629</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.03631876443315511</v>
+        <v>0.006709813189988085</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1084951974620932</v>
+        <v>0.01280862712365495</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.08717166272743332</v>
+        <v>0.02322241762389409</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.01235817142517943</v>
+        <v>0.01806544303287232</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.03440654406264015</v>
+        <v>-0.01395451907637029</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,34 +6537,34 @@
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.008907800445750657</v>
+        <v>-0.01243226492569876</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.004399102494548317</v>
+        <v>0.0117471549540659</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1047370057322039</v>
+        <v>-0.01847266298771004</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01914548170946802</v>
+        <v>-0.007174946101795729</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6576,13 +6576,13 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.01485141860426576</v>
+        <v>0.03162373625837871</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1182367563524874</v>
+        <v>-0.04666858508420466</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,13 +6591,13 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.03319979597720287</v>
+        <v>-0.003532538607794533</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6606,10 +6606,10 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.04879575787577533</v>
+        <v>0.02054990191291621</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.05408039401192199</v>
+        <v>-0.02606199457220477</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.08793089961423908</v>
+        <v>0.02227614768801659</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6627,31 +6627,31 @@
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.04258302787323238</v>
+        <v>0.003674797648748396</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03929665386912452</v>
+        <v>0.004751186228594659</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.008417817807125007</v>
+        <v>0.008121243312028565</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>-0</v>
@@ -6660,10 +6660,10 @@
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.07957161118919936</v>
+        <v>0.02533419125468746</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05231683463534471</v>
+        <v>-0.02048470848906481</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6675,42 +6675,42 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF11" t="n">
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3415514966458008</v>
+        <v>0.003263200021833188</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05987241321972574</v>
+        <v>-0.001412162987328054</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1212770365090693</v>
+        <v>-0.001094455616842419</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,25 +6719,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1970972272572605</v>
+        <v>0.004278661083993044</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0767720471228422</v>
+        <v>-0.001239967109419061</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.09026116686894002</v>
+        <v>-0.001396814853290077</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,88 +6746,88 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1369491858146346</v>
+        <v>0.0004449900704951245</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09772895390758969</v>
+        <v>-0.00120023325043483</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.02960401965795932</v>
+        <v>-2.438799445941941e-05</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04379197919354457</v>
+        <v>-6.085828079589141e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00586778757728071</v>
+        <v>-0.0001870903348053988</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.436090362232546e-13</v>
+        <v>-1.003998667386854e-13</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.08414764576320176</v>
+        <v>0.001296218066149037</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03063664236672827</v>
+        <v>8.20977109029349e-05</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.06961103336264543</v>
+        <v>-0.0003436165770563132</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4720946925883336</v>
+        <v>0.006203708193188557</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,25 +6836,25 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08259717405793482</v>
+        <v>-0.0006798858298965668</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.08382232692156831</v>
+        <v>-0.0005658915415701108</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0654141966932334</v>
+        <v>-0.001662361705328776</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.146005208341475</v>
+        <v>-0.001260836776935403</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.07095597978758073</v>
+        <v>-0.0002502144081304155</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.002366086193398574</v>
+        <v>0.0004776535128884942</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.07367222442108862</v>
+        <v>0.003195063051729583</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.05709567735314711</v>
+        <v>0.0003377438537357188</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2152668213115117</v>
+        <v>0.004080946404936055</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01421893667494718</v>
+        <v>-0.0008107023011237614</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.04919836208327753</v>
+        <v>-0.000239207726310208</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1056656352745827</v>
+        <v>-0.001778310675747451</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.003337534779917592</v>
+        <v>0.000676097378468196</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.04178483193514076</v>
+        <v>0.0002687924154071556</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0452389736237582</v>
+        <v>-0.001304509211734323</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.04502092263144209</v>
+        <v>2.490503316335736e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.005738084025857479</v>
+        <v>-0.0005600950689518461</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,25 +6986,25 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09908585918659761</v>
+        <v>-0.001885927943950561</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.006238431709342388</v>
+        <v>0.0004119987969586555</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.04711285676169643</v>
+        <v>0.000554196998622302</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.2329864090880344</v>
+        <v>-0.0009869875131525753</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
@@ -7025,52 +7025,52 @@
         <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05570608745279546</v>
+        <v>-0.0007920196718365268</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.03480049417973468</v>
+        <v>-0.0005716246651952127</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.007059779686927379</v>
+        <v>-0.0008455344497932298</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01393395898694593</v>
+        <v>1.608484109150447e-05</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.01177372856978751</v>
+        <v>0.0006192305507294235</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.08280815804559229</v>
+        <v>0.001624021134635357</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.03190468650863516</v>
+        <v>-0.0004517927881252135</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.008062422711113466</v>
+        <v>0.0003567989878058162</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,25 +7094,25 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.04472951453214273</v>
+        <v>-0.001275468338187074</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.03147638773710253</v>
+        <v>0.0004167386312750419</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.03671949032698358</v>
+        <v>-0.0002301688936515398</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7124,49 +7124,49 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07473376487879467</v>
+        <v>-0.0009862032585248163</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.009396700169150493</v>
+        <v>1.916899001556581e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0.00909030006615771</v>
+        <v>-0.0002013352295834757</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1058395788155789</v>
+        <v>-0.002081906996597658</v>
       </c>
       <c r="EZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02131028776560923</v>
+        <v>0.0002254691104629734</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.04672113474762873</v>
+        <v>0.0002904969834255447</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,37 +7175,37 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.06680534733891758</v>
+        <v>-0.0001027586418989578</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.06208347784782419</v>
+        <v>0.0002940659381072231</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.03119152395862422</v>
+        <v>-9.640650091458512e-05</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.0149767313261869</v>
+        <v>8.454562650820726e-05</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,46 +7214,46 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.005232407404600471</v>
+        <v>0.0003088788178066462</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.06150084433315758</v>
+        <v>0.0005562330752855004</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.06988852365815514</v>
+        <v>-0.001632384969930132</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0.07037210843434419</v>
+        <v>0.0005210386418261319</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4940848067229939</v>
+        <v>0.995290080643652</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1556707240961142</v>
+        <v>-0.3386024244867957</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2113018654625718</v>
+        <v>-0.1970460224280068</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3077829916219924</v>
+        <v>1.11866969011118</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1810962509662244</v>
+        <v>-0.3215330411345179</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -7306,28 +7306,28 @@
         <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1699307642707485</v>
+        <v>-0.1141583104316127</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1908462999132181</v>
+        <v>0.2094152469073502</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03915750965719401</v>
+        <v>-0.3149587140942211</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
@@ -7336,76 +7336,76 @@
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.05363557702180044</v>
+        <v>-0.2626946507475998</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05163563972683565</v>
+        <v>0.03628305723471912</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.008129089255700274</v>
+        <v>-0.09244831026828855</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.002825772657178147</v>
+        <v>0.003414730807995887</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1210527973473092</v>
+        <v>0.4804514598714231</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01626450935588715</v>
+        <v>0.2246096327506148</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.05341220890147508</v>
+        <v>-0.08257838290080027</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6003596630656459</v>
+        <v>1.722328570109727</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1010110057600429</v>
+        <v>-0.2415799821541386</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7417,13 +7417,13 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.1759626023047828</v>
+        <v>0.003101508031208537</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1065828136399348</v>
+        <v>-0.3189351353397684</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.2895850914223399</v>
+        <v>-0.329805551246225</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.1445764838589528</v>
+        <v>-0.148334425098925</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.04551499332200066</v>
+        <v>0.08587882366798372</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,52 +7459,52 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.2156227848496671</v>
+        <v>0.2109474092626598</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.003010156642644035</v>
+        <v>0.1210929559773549</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.3520641780971481</v>
+        <v>1.122239709309238</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.01571103973742782</v>
+        <v>-0.2470389926085048</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.06497944448137635</v>
+        <v>-0.2586083576175648</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.148330876035297</v>
+        <v>-0.5731976778320858</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,25 +7513,25 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.005980381114792039</v>
+        <v>0.1152266859092199</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.09949941009239956</v>
+        <v>0.09239202183056749</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.07953155588326682</v>
+        <v>-0.4380477897575068</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,7 +7540,7 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04418803264317025</v>
+        <v>0.07772828407158222</v>
       </c>
       <c r="CR13" t="n">
         <v>-0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.02080527379596706</v>
+        <v>0.06234856121082344</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1306142630132254</v>
+        <v>-0.5604319643372065</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005735740808937768</v>
+        <v>0.07676561026125377</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0776680065575049</v>
+        <v>0.1592129285231625</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1850186325087347</v>
+        <v>-0.2101157999249314</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01884111295873396</v>
+        <v>0.07071867016894146</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7603,25 +7603,25 @@
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.001501331977913584</v>
+        <v>-0.1532693212302406</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.01863234106622962</v>
+        <v>-0.3059702004530451</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.007528892375356588</v>
+        <v>0.06451707767798448</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,124 +7630,124 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.006425750067442979</v>
+        <v>-0.1641904130437563</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1032443968463352</v>
+        <v>0.3554681130223526</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.04373245824401272</v>
+        <v>-0.221803979232642</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0.0002569892388709924</v>
+        <v>0.1650680426321778</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.05482021241611838</v>
+        <v>-0.2839482307386916</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02420375537790847</v>
+        <v>-0.07054136692571045</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.1284321881389089</v>
+        <v>0.08918931591954808</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1244504007755015</v>
+        <v>-0.3319898509061475</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02418958060514468</v>
+        <v>-0.01316936852033992</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.07087522938713864</v>
+        <v>0.1763449729358031</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1516891220406906</v>
+        <v>-0.6425159998183254</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.009147080558182901</v>
+        <v>0.06258087688150642</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.07867804424159633</v>
+        <v>0.1479470178511783</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.08670814401796181</v>
+        <v>-0.218593508678428</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.06410916916761182</v>
+        <v>-0.08988400153587048</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.0357218924941721</v>
+        <v>-0.1810261776445644</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02463184115138704</v>
+        <v>-0.0536352339085876</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,7 +7783,7 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.00612399302497947</v>
+        <v>0.03479896230721768</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7792,37 +7792,37 @@
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.006005854261766714</v>
+        <v>-0.1513887748915959</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.1043109663002531</v>
+        <v>-0.2731236013876229</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.02146843487910407</v>
+        <v>0.1677956765796951</v>
       </c>
     </row>
     <row r="14">
@@ -8399,16 +8399,16 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4408189616825194</v>
+        <v>-0.6324741728496693</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4857436483879309</v>
+        <v>0.2298237636761775</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0001208377023675562</v>
+        <v>0.2667902740872209</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8426,25 +8426,25 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3087116600858973</v>
+        <v>-0.7306281460809427</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3583905892554451</v>
+        <v>0.1839908134131542</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2090874964937682</v>
+        <v>0.1842316164640409</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
@@ -8453,16 +8453,16 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1268263960429287</v>
+        <v>-0.2024983850760656</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01122975220054954</v>
+        <v>-0.1280954560477353</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.04769217841188785</v>
+        <v>-0.08223350024899811</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8471,106 +8471,106 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.08555077676928874</v>
+        <v>-0.01242288911682277</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.0002111815623978148</v>
+        <v>0.1042626153631848</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.0525606753191706</v>
+        <v>0.03696145080935544</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.2448814962092515</v>
+        <v>-0.3394616700582709</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.06792721213575587</v>
+        <v>0.03080804717162754</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01444006519919969</v>
+        <v>-0.3582124039464906</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.4669255449430049</v>
+        <v>-0.9722063523476022</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.339746320626391</v>
+        <v>-0.05297208552640742</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.1471355699317606</v>
+        <v>-0.04187268178789373</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.08600552547067963</v>
+        <v>0.3804047743587684</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.174965901881208</v>
+        <v>0.2585668762033214</v>
       </c>
       <c r="BF15" t="n">
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.376822756907503</v>
+        <v>0.5489031637523909</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8588,25 +8588,25 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.05125753107376308</v>
+        <v>0.08455707552803057</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.08945819751303594</v>
+        <v>0.01302817136672182</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.1183041894332046</v>
+        <v>-0.0312102777248937</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,19 +8615,19 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.1598786474952575</v>
+        <v>-0.6260802267190573</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.3386565978309464</v>
+        <v>-0.03897853354261757</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.05611973783793379</v>
+        <v>-0.07410343815232388</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8636,31 +8636,31 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1349789819307364</v>
+        <v>0.3767249521069816</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0.07769610865101886</v>
+        <v>-0.08658634949797006</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.02440780407761631</v>
+        <v>-0.07416074391901262</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02722711563298532</v>
+        <v>0.25332404324523</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.01207239363536748</v>
+        <v>-0.03490887002697092</v>
       </c>
       <c r="CP15" t="n">
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.09161554795852025</v>
+        <v>-0.1174541444800802</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8693,28 +8693,28 @@
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.09908876134357367</v>
+        <v>0.3568754099481097</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.07839288106123145</v>
+        <v>-0.06631577952152855</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.004868474738878039</v>
+        <v>-0.05231102843445953</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
@@ -8723,103 +8723,103 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1254166645390838</v>
+        <v>0.08099436724270334</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.03296181275590543</v>
+        <v>0.06846801961149111</v>
       </c>
       <c r="DH15" t="n">
         <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1213513130239793</v>
+        <v>0.05324418222286678</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM15" t="n">
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.006497859947220424</v>
+        <v>0.1647387377302777</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0.008665938313251725</v>
+        <v>-0.07073418782533587</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.1064606393768627</v>
+        <v>-0.05583826014035247</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06841640563289295</v>
+        <v>-0.2123021690934652</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.05709292354164554</v>
+        <v>0.006769350848660983</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.03758418037624453</v>
+        <v>0.1695609083697629</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE15" t="n">
         <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.02205391221764075</v>
+        <v>0.2240820528617462</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.0677272332608385</v>
+        <v>0.09737030698450033</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.06412815077385257</v>
+        <v>-0.07235632885515057</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM15" t="n">
         <v>0</v>
@@ -8828,19 +8828,19 @@
         <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.08221775854720045</v>
+        <v>0.241516139381046</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0202747506390775</v>
+        <v>0.04634692347691685</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.004297273401385887</v>
+        <v>0.01139659513300526</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
@@ -8849,34 +8849,34 @@
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1152589217846858</v>
+        <v>0.4131894743904803</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0.06568982865213743</v>
+        <v>-0.07906025359711927</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.03109467287299124</v>
+        <v>-0.07309918587997978</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,19 +8885,19 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.09148619382358507</v>
+        <v>0.1289955445094301</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1221835532620295</v>
+        <v>0.2220755817463901</v>
       </c>
       <c r="FJ15" t="n">
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.1793878853206186</v>
+        <v>0.2119468291522048</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM15" t="n">
         <v>-0</v>
@@ -8906,49 +8906,49 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>9.471605467331808e-05</v>
+        <v>0.001677743533704455</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0.05953444839317886</v>
+        <v>-0.002034845900764175</v>
       </c>
       <c r="FS15" t="n">
         <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01317976874406395</v>
+        <v>-0.02175856288938069</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.06136190134482987</v>
+        <v>0.1813175972510336</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0.001092664928008966</v>
+        <v>0.2104459475503317</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1496082658998431</v>
+        <v>0.3050360095745513</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05050764279610264</v>
+        <v>0.06400158013401473</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07783150167930862</v>
+        <v>-0.1674769457784007</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1084893438066814</v>
+        <v>0.3220272473673892</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,16 +9004,16 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0206292743286881</v>
+        <v>-0.04571577325023095</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.05058132542063425</v>
+        <v>-0.1470264742236829</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9022,49 +9022,49 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02334656483461089</v>
+        <v>0.1307925820487379</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01685320739660771</v>
+        <v>-0.03629736835018972</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0005317449149046421</v>
+        <v>0.001249656014089701</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0008385756378535438</v>
+        <v>-0.01662695934095518</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.006659123548114939</v>
+        <v>-0.0568962331595159</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003159968205281028</v>
+        <v>0.02126784312271769</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,34 +9076,34 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02344061157875744</v>
+        <v>0.09693679564203371</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.002593447887551928</v>
+        <v>-0.03597150667206924</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.03903432690755655</v>
+        <v>-0.06297048187075689</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1136875712437861</v>
+        <v>0.5815704534895814</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,25 +9112,25 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.03927614719870123</v>
+        <v>-0.209841477600869</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.09202787207415655</v>
+        <v>-0.2608453366049366</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03546575413379773</v>
+        <v>-0.1438077140173589</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,70 +9139,70 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.0357400211000821</v>
+        <v>0.002736302381433662</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02229286350805137</v>
+        <v>-0.06537678521096568</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.02482467292587764</v>
+        <v>0.1330822170123771</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.002546648575107513</v>
+        <v>0.08781500073323319</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.00642027549446862</v>
+        <v>0.04154053642638391</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.06189139438839626</v>
+        <v>0.3211102710153835</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.02653877200269847</v>
+        <v>-0.0408279562914721</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.02640025337916411</v>
+        <v>-0.09459072376677409</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
@@ -9211,34 +9211,34 @@
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.0311781498043518</v>
+        <v>-0.1293280273265344</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.001258627113071169</v>
+        <v>0.0143163492904592</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02452932073712738</v>
+        <v>0.05694484722510691</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.005738668127066465</v>
+        <v>-0.1248799943468115</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,37 +9247,37 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.0005489756660519262</v>
+        <v>0.08676040793352575</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01799896468366113</v>
+        <v>0.01934352001336341</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.02854765388914949</v>
+        <v>-0.121853981263481</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.003458761725712044</v>
+        <v>-0.006596791421021745</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03034752932369078</v>
+        <v>0.09029453842520681</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9286,40 +9286,40 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.02038873561903875</v>
+        <v>-0.1264886436581259</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04198357010656961</v>
+        <v>-0.1615775342278365</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.0009766352999453886</v>
+        <v>0.05476920091127242</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.00963550648505076</v>
+        <v>-0.08130355478301605</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
@@ -9328,37 +9328,37 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.013568503397487</v>
+        <v>0.01310651678105894</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.000199566948178412</v>
+        <v>0.08248656422432123</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02125698854071172</v>
+        <v>-0.1140297928281721</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.007038951875142824</v>
+        <v>0.01022053976577308</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.008982954013516599</v>
+        <v>0.03711994863384966</v>
       </c>
       <c r="EC16" t="n">
         <v>0</v>
@@ -9367,25 +9367,25 @@
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.03249091348122058</v>
+        <v>-0.03528280158771884</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.01244890074491323</v>
+        <v>-0.0335965439248038</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.03448664767752143</v>
+        <v>-0.03569887343870646</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9400,22 +9400,22 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01780821487346118</v>
+        <v>-0.01155727800894668</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.0009834098558741153</v>
+        <v>-0.08928045134940379</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.009587972805082567</v>
+        <v>-0.02867918146376466</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9427,46 +9427,46 @@
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.02666139601646762</v>
+        <v>-0.1514071899892321</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.003533873754926275</v>
+        <v>-0.01409304341797898</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02634767334706528</v>
+        <v>0.06864013689897967</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.001280893963123695</v>
+        <v>0.09563859468352894</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01007008216087361</v>
+        <v>-0.03238144428424074</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.03176563858496266</v>
+        <v>0.1261001429295096</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
@@ -9478,10 +9478,10 @@
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.00281222217637857</v>
+        <v>-0.0277405752607051</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,43 +9490,43 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01125035671199754</v>
+        <v>0.05554611827105121</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01700353811588047</v>
+        <v>-0.0895617121026107</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.004676091419725967</v>
+        <v>-0.05214476896110549</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.01839851382954323</v>
+        <v>0.09411891491589483</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>-0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1020841332879855</v>
+        <v>0.1526417087678394</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,40 +9546,40 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08402052929767165</v>
+        <v>-0.04405886601086263</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0169935866552945</v>
+        <v>-0.05981421938115108</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06421677013463198</v>
+        <v>0.1637992852416496</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05771565482580825</v>
+        <v>-0.07902204596326383</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.01306626349716746</v>
+        <v>-0.05600794788109285</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9588,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02156141023026783</v>
+        <v>0.06231846372131986</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.008322170071173819</v>
+        <v>-0.05466236353752718</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01045900277248337</v>
+        <v>0.003164034593307104</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.003494791878018157</v>
+        <v>-0.02371477780636356</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.003611691802032547</v>
+        <v>-0.06230904846397898</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.003468238058667024</v>
+        <v>0.00555231336475926</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -9642,28 +9642,28 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01693600797579485</v>
+        <v>0.01683485723967399</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01312647997872498</v>
+        <v>-0.0437589812754258</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01509425824321281</v>
+        <v>0.004398188360805986</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -9672,7 +9672,7 @@
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.09172262013028937</v>
+        <v>0.2074253403035326</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,10 +9681,10 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.04856937190885982</v>
+        <v>-0.1288116338023894</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.0144052958861114</v>
+        <v>-0.1069601757748156</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -9693,13 +9693,13 @@
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0195207084017245</v>
+        <v>-0.02065822284424913</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,64 +9708,64 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.05422323863266254</v>
+        <v>-0.01425059198536224</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.01060783340913262</v>
+        <v>-0.01378818716350386</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.02513539238880621</v>
+        <v>0.02942306444989923</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01462339514021655</v>
+        <v>0.06188401198311964</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0153860614232823</v>
+        <v>0.02238019032467169</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.04914350702308985</v>
+        <v>0.1248429803318388</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02666337425894548</v>
+        <v>-0.03915003073539105</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.002590875586360009</v>
+        <v>-0.03214712190446828</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9774,40 +9774,40 @@
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.01814226709795432</v>
+        <v>-0.0419082847597705</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.01381361616338777</v>
+        <v>0.02690499250766374</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.006292756465611227</v>
+        <v>0.03597608880649066</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>-0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0003910181451737072</v>
+        <v>-0.03340721576637444</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,37 +9816,37 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.002831175779817538</v>
+        <v>0.05324666581245086</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.007262926825804069</v>
+        <v>0.02047171867909928</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01279802266547996</v>
+        <v>-0.04324501792446724</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0122677994742888</v>
+        <v>0.02197854092911719</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.01174170143216478</v>
+        <v>0.05166613967004771</v>
       </c>
       <c r="DB17" t="n">
         <v>-0</v>
@@ -9855,25 +9855,25 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01421292064359185</v>
+        <v>-0.04329792637302853</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0181035049481498</v>
+        <v>-0.04405949083624984</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.00294719262654576</v>
+        <v>0.0152685473126377</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -9882,106 +9882,106 @@
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.004275381857019834</v>
+        <v>0.007095946239171823</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.02153534443819882</v>
+        <v>-0.02386975835392742</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.009109462437326936</v>
+        <v>-0.01317855735874414</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.01956926762507731</v>
+        <v>-0.008242463904672601</v>
       </c>
       <c r="DY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01936645685144719</v>
+        <v>-0.003409090674396716</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.004632107804889072</v>
+        <v>0.02712466787466808</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.02045058312696749</v>
+        <v>-0.02382702979715013</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01249634226870981</v>
+        <v>0.01579363437080824</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.009048908578283589</v>
+        <v>0.01015815764016457</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.002809502266768191</v>
+        <v>-0.02416843350541758</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.006389502698110698</v>
+        <v>0.01950102461616521</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.004764912773717733</v>
+        <v>0.05259189920909937</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9990,25 +9990,25 @@
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01221428599050072</v>
+        <v>-0.04862495502780667</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.01293285921557576</v>
+        <v>0.01479844806877751</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.01223946426423255</v>
+        <v>0.03404565480886572</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
@@ -10020,10 +10020,10 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.00403781842391285</v>
+        <v>0.05805849620830821</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,16 +10032,16 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.01522466675568582</v>
+        <v>-0.02526074963024479</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01344791572013587</v>
+        <v>0.02753451299386094</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.002808898544490414</v>
+        <v>-0.01184390393513543</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,40 +10059,40 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.00750255434764861</v>
+        <v>0.02013282042754272</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.008923002870434887</v>
+        <v>-0.05632865238998719</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.005217629771249037</v>
+        <v>-0.03858203107362491</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.008427603097652331</v>
+        <v>0.05626918471806199</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>-0</v>
@@ -10103,49 +10103,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3908482284799203</v>
+        <v>0.27906341140928</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1415305532121398</v>
+        <v>-0.1721047405623718</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.03734246700600252</v>
+        <v>-0.05382423867111009</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
         <v>-0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2684824886632711</v>
+        <v>0.2817095067108163</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1467026088088991</v>
+        <v>-0.2178468124267593</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05606121135248502</v>
+        <v>-0.09647993297298611</v>
       </c>
       <c r="O18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>-0</v>
@@ -10154,139 +10154,139 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1025781878612301</v>
+        <v>0.05092960879709795</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.005887372055981032</v>
+        <v>-0.03742790870700537</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1023360302370037</v>
+        <v>-0.0171264904303167</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1019684851844056</v>
+        <v>-0.004663533305219917</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.01040495651815334</v>
+        <v>-0.03984156522691736</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.003349430925435355</v>
+        <v>-0.02678072304639451</v>
       </c>
       <c r="AG18" t="n">
         <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.01435144831739498</v>
+        <v>0.05565911060018083</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.07636656378673791</v>
+        <v>-0.03304216043460818</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.08922455505332197</v>
+        <v>0.0367403440813706</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.3359384194582907</v>
+        <v>0.221396695599989</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.07319756489617422</v>
+        <v>-0.1554939418839317</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.1419134082802872</v>
+        <v>-0.1579171260080268</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02797713467093448</v>
+        <v>0.002010825938985683</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.05805134466920195</v>
+        <v>-0.05721859337844349</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1169422629402479</v>
+        <v>-0.003745060216452424</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
@@ -10295,19 +10295,19 @@
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05694798247597166</v>
+        <v>0.001550845906381617</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.05899851120585817</v>
+        <v>0.07723452355695716</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1979007751952771</v>
+        <v>0.04788186151710333</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
         <v>0</v>
@@ -10316,22 +10316,22 @@
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1604826507973125</v>
+        <v>0.1761781259607639</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.01855643253586027</v>
+        <v>-0.111658041366504</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.09865811961175174</v>
+        <v>-0.02389575488586959</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -10340,106 +10340,106 @@
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.08985607678154689</v>
+        <v>-0.07788387425564711</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.02646568059917847</v>
+        <v>0.09937519027483141</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.01216717102087097</v>
+        <v>0.01030230388279605</v>
       </c>
       <c r="CI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.02373886836111925</v>
+        <v>-0.05365453480748476</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.06123675580626253</v>
+        <v>0.1145605739243254</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.1073901702012416</v>
+        <v>0.04883081840980789</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.08553426522495343</v>
+        <v>-0.08834934784503301</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.04541795342960152</v>
+        <v>0.1145525159808156</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.004737652662853742</v>
+        <v>0.01894685971002438</v>
       </c>
       <c r="DA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.01167532022366577</v>
+        <v>-0.03018910362918232</v>
       </c>
       <c r="DG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.00522976608010529</v>
+        <v>0.02255883947343936</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.008584961919464862</v>
+        <v>-0.04433147355759415</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
@@ -10454,19 +10454,19 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.006211831031062068</v>
+        <v>-0.03911175051430004</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0.1762713406829348</v>
+        <v>0.02841086132839993</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.04817659476881336</v>
+        <v>0.005100622281625763</v>
       </c>
       <c r="DS18" t="n">
         <v>-0</v>
@@ -10475,85 +10475,85 @@
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.06411067244608598</v>
+        <v>-0.02634008135294045</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.009830828483425074</v>
+        <v>0.03298517806692933</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.03959695257008852</v>
+        <v>-0.04846634956167581</v>
       </c>
       <c r="EB18" t="n">
         <v>0</v>
       </c>
       <c r="EC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.1085980045543459</v>
+        <v>-0.0634134743568055</v>
       </c>
       <c r="EH18" t="n">
         <v>0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.08250780357661347</v>
+        <v>0.08967125266665757</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.07410638221299015</v>
+        <v>0.02648468372586095</v>
       </c>
       <c r="EK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.09174763403608648</v>
+        <v>-0.03152943386805694</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.08213835254051061</v>
+        <v>0.06389111200061728</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.01346117157503463</v>
+        <v>-0.0114215228907196</v>
       </c>
       <c r="ET18" t="n">
         <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10565,43 +10565,43 @@
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.08093175669359416</v>
+        <v>-0.101879262727118</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.0301811700528325</v>
+        <v>0.118328371998942</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.002043848056553023</v>
+        <v>0.01088325071226271</v>
       </c>
       <c r="FC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD18" t="n">
         <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF18" t="n">
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.03017341466913788</v>
+        <v>0.06845673470906528</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>-0.08295084516729991</v>
+        <v>-0.1027733631118575</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.03856790091758881</v>
+        <v>-0.004776499118770632</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10613,22 +10613,22 @@
         <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.01315159667940698</v>
+        <v>-0.02651647477654762</v>
       </c>
       <c r="FR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.1149543109851126</v>
+        <v>0.09113220629235091</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.005635113998638619</v>
+        <v>0.05896616290262913</v>
       </c>
       <c r="FU18" t="n">
         <v>-0</v>
@@ -10646,25 +10646,25 @@
         <v>-0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.0118155659803467</v>
+        <v>-0.03810200020311424</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.06156492650544612</v>
+        <v>0.05435217845283753</v>
       </c>
       <c r="GC18" t="n">
         <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG18" t="n">
         <v>-0</v>
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2146974991055687</v>
+        <v>0.4373872719203684</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -11253,13 +11253,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.06166249570091765</v>
+        <v>0.1166710417576716</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1372065465011049</v>
+        <v>-0.2320435110246692</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>-0</v>
@@ -11271,25 +11271,25 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1651538173850599</v>
+        <v>0.5463597474224761</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.03101471768801332</v>
+        <v>0.03738929178112004</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1097344187097961</v>
+        <v>-0.1683664257590028</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -11298,7 +11298,7 @@
         <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02379762877177963</v>
+        <v>0.1384588586210726</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -11307,16 +11307,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.01635128109844269</v>
+        <v>-0.1191741736161786</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.004275735685908793</v>
+        <v>-0.03541747817658387</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -11325,22 +11325,22 @@
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.006215450076922325</v>
+        <v>0.007887111454452754</v>
       </c>
       <c r="AD20" t="n">
         <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.01330545012385246</v>
+        <v>-0.2957807775175201</v>
       </c>
       <c r="AG20" t="n">
-        <v>-7.992590638328244e-05</v>
+        <v>-0.0907955681389889</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>-0</v>
@@ -11352,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.03052688726185477</v>
+        <v>0.1301198132250574</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -11361,10 +11361,10 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.00331143344402303</v>
+        <v>-0.02788449165221842</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.03842386836336169</v>
+        <v>-0.09144642039184242</v>
       </c>
       <c r="AQ20" t="n">
         <v>-0</v>
@@ -11376,10 +11376,10 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.1481128656561646</v>
+        <v>0.6675610584297661</v>
       </c>
       <c r="AV20" t="n">
         <v>-0</v>
@@ -11388,25 +11388,25 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.02382546226205735</v>
+        <v>-0.07582594835978024</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.07844487785598281</v>
+        <v>-0.1034894064737233</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.04047987357956814</v>
+        <v>-0.09997509534723616</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
@@ -11415,64 +11415,64 @@
         <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.0547000783482053</v>
+        <v>-0.07709411701546948</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.0534923858599631</v>
+        <v>-0.133600117950018</v>
       </c>
       <c r="BI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.03926529050770443</v>
+        <v>0.129185666080984</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
         <v>-0</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.0005786439610635845</v>
+        <v>0.08863890593199711</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.0195468211318834</v>
+        <v>-0.02304378903845352</v>
       </c>
       <c r="BR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.07153860270920621</v>
+        <v>0.3680117004449046</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX20" t="n">
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.02562032553457219</v>
+        <v>-0.03779317210690522</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-0.0493928857213525</v>
+        <v>-0.1600603324317908</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
@@ -11487,154 +11487,154 @@
         <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.03638933104603533</v>
+        <v>-0.1535878669499456</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
         <v>-0</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.003425098364924364</v>
+        <v>0.02009266893724536</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.03078446949301888</v>
+        <v>0.09292093522574893</v>
       </c>
       <c r="CJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.006472712784301688</v>
+        <v>-0.2689707929397192</v>
       </c>
       <c r="CO20" t="n">
         <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.005258313761749181</v>
+        <v>0.1314915037980961</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.01446408998899489</v>
+        <v>0.09621625686236646</v>
       </c>
       <c r="CS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.027784736787574</v>
+        <v>-0.1432577612998865</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
         <v>0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.005347740411477608</v>
+        <v>-0.01873411204436209</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.03427269020423423</v>
+        <v>0.1186474781200755</v>
       </c>
       <c r="DB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC20" t="n">
         <v>-0</v>
       </c>
       <c r="DD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.01034246398226128</v>
+        <v>-0.05145855742107339</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.02967893283345814</v>
+        <v>-0.2355266129709956</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.001847564716961329</v>
+        <v>0.05962143512777236</v>
       </c>
       <c r="DK20" t="n">
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.005260052249227066</v>
+        <v>-0.05974444202084379</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ20" t="n">
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.02408550440186001</v>
+        <v>0.001688498373567673</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.0002697735698777041</v>
+        <v>-0.01879478202999783</v>
       </c>
       <c r="DT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW20" t="n">
         <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.0204188512343726</v>
+        <v>-0.06575291088250412</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
         <v>-0</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.008115893331866209</v>
+        <v>-0.1893356872725337</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.02432746877151867</v>
+        <v>0.08807557440103797</v>
       </c>
       <c r="EC20" t="n">
         <v>-0</v>
@@ -11646,37 +11646,37 @@
         <v>-0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.03967894479605003</v>
+        <v>0.007377219792398275</v>
       </c>
       <c r="EH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI20" t="n">
         <v>0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.01010139768537819</v>
+        <v>-0.08259169066525363</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.03197284549126673</v>
+        <v>0.005439913652093229</v>
       </c>
       <c r="EL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM20" t="n">
         <v>-0</v>
       </c>
       <c r="EN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.01394165763703744</v>
+        <v>-0.0457546644988298</v>
       </c>
       <c r="EQ20" t="n">
         <v>0</v>
@@ -11685,79 +11685,79 @@
         <v>-0</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.01371775719449716</v>
+        <v>-0.04782281586294252</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.01457573055335869</v>
+        <v>0.08862605194867484</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.02647403098958084</v>
+        <v>-0.169186112108647</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA20" t="n">
         <v>-0</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.004349198245360052</v>
+        <v>-0.05256741744794888</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.03124462316982133</v>
+        <v>0.1053090801395038</v>
       </c>
       <c r="FD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE20" t="n">
         <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.0008561665074462474</v>
+        <v>0.185564864074029</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
         <v>-0</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.003133390353812409</v>
+        <v>-0.1469938755066164</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.02123038162692813</v>
+        <v>-0.1839214040883827</v>
       </c>
       <c r="FM20" t="n">
         <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>-0.006582759523880407</v>
+        <v>-0.1150309422622585</v>
       </c>
       <c r="FR20" t="n">
         <v>-0</v>
@@ -11766,46 +11766,46 @@
         <v>-0</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.003925724811692122</v>
+        <v>0.04536955963132481</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.04553411504432513</v>
+        <v>-0.1387912373771158</v>
       </c>
       <c r="FV20" t="n">
         <v>-0</v>
       </c>
       <c r="FW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.02114471914552674</v>
+        <v>0.02789721559144994</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
         <v>-0</v>
       </c>
       <c r="GC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0.01705513389702289</v>
+        <v>0.04492026981423372</v>
       </c>
       <c r="GE20" t="n">
         <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
